--- a/data/inst_2.xlsx
+++ b/data/inst_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\flexible-vrp\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TFG\Flexible\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C197B6B6-AB4E-4DA2-BE85-8FDFA731D9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D4A9D6-0333-467E-A854-53BFDA03E0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5A598FCB-B967-4DAF-9410-AD9F1FA49DAC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{5A598FCB-B967-4DAF-9410-AD9F1FA49DAC}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="3" r:id="rId1"/>
@@ -495,9 +495,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -535,7 +535,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -641,7 +641,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -783,7 +783,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -792,12 +792,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118A7758-BA92-46A5-BE73-1AD0F0A01B68}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -805,7 +805,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -813,15 +813,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -829,7 +829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -837,7 +837,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -845,7 +845,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -853,7 +853,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -861,7 +861,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -869,7 +869,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -877,7 +877,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -886,15 +886,15 @@
         <v>17.857142857142858</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -902,7 +902,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -918,9 +918,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A54DE7-45BC-48AF-A573-13FFF226C261}">
   <dimension ref="A1:C57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -931,7 +931,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -942,7 +942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -953,7 +953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -964,7 +964,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -975,7 +975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -986,7 +986,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -997,7 +997,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>7</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -1555,9 +1555,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E770ECA-E10C-4651-A068-F1B5FC905D1A}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
